--- a/inasistencias-4b-elecYsiscom-tp/alumnos-4b-ElecYsisCom-tp.xlsx
+++ b/inasistencias-4b-elecYsiscom-tp/alumnos-4b-ElecYsisCom-tp.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="164">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">Exposicion</t>
   </si>
   <si>
+    <t xml:space="preserve">nota </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ivan</t>
   </si>
   <si>
@@ -352,6 +355,18 @@
     <t xml:space="preserve">Evaluacion</t>
   </si>
   <si>
+    <t xml:space="preserve">le agregaron una bateria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">maqueta con sistema de riego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">acumular extra </t>
+  </si>
+  <si>
     <t xml:space="preserve">explicar generador de continua</t>
   </si>
   <si>
@@ -367,52 +382,40 @@
     <t xml:space="preserve">se consiguio modelo para impresora 3d, para la proxima la pila funcionando</t>
   </si>
   <si>
+    <t xml:space="preserve">automatizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filtro externo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Traer rectificador </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rectificador completo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hacer 4 pancho pilas para prender</t>
   </si>
   <si>
     <t xml:space="preserve">presentacion con bornes</t>
   </si>
   <si>
+    <t xml:space="preserve">acumulacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">donde acumular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imagen vifual?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">se compromete para la semana que viene </t>
+  </si>
+  <si>
     <t xml:space="preserve">separar los bornes</t>
   </si>
   <si>
     <t xml:space="preserve">aporte de tevez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">le agregaron una bateria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feria </t>
-  </si>
-  <si>
-    <t xml:space="preserve">maqueta con sistema de riego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acumular extra </t>
-  </si>
-  <si>
-    <t xml:space="preserve">automatizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">filtro externo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Traer rectificador </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rectificador completo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acumulacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">donde acumular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imagen vifual?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se compromete para la semana que viene </t>
   </si>
   <si>
     <t xml:space="preserve">Finalizado</t>
@@ -606,15 +609,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -627,7 +630,54 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="13">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCC0000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCFFCC"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF006600"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -681,6 +731,52 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FF006600"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCCFFCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <color rgb="FFCC0000"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <charset val="1"/>
+        <family val="0"/>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="12"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFCC0000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -723,7 +819,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFCCCC"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -856,14 +952,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AK19"/>
   <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.47"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="31.19"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="5" style="1" width="14.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.77"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="6" style="1" width="8.61"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="15" style="1" width="8.61"/>
@@ -874,8 +970,10 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="25" style="1" width="8.71"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="1" width="56.3"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="8.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="65.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="20.92"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="29" style="1" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="65.64"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="33" min="31" style="1" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="20.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -977,14 +1075,20 @@
       <c r="AF2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AG2" s="3" t="n">
         <v>45947</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AH2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -992,40 +1096,40 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N3" s="1" t="n">
         <f aca="false">COUNTIF(F3:M3,"P")</f>
@@ -1036,56 +1140,62 @@
         <v>1</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T3,R3,P3,N3,L3),0)</f>
         <v>6</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>8</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z3" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC3" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH3" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI3" s="5" t="s">
+      <c r="AG3" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1093,37 +1203,37 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N4" s="1" t="n">
         <f aca="false">COUNTIF(F4:M4,"P")</f>
@@ -1134,35 +1244,41 @@
         <v>0</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T4,R4,P4,N4,L4),0)</f>
         <v>6</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC4" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH4" s="0" t="n">
-        <v>8</v>
+      <c r="AG4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1170,37 +1286,37 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N5" s="1" t="n">
         <f aca="false">COUNTIF(F5:M5,"P")</f>
@@ -1211,38 +1327,44 @@
         <v>0</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T5,R5,P5,N5,L5),0)</f>
         <v>6</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH5" s="0" t="n">
-        <v>8</v>
+      <c r="AG5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1250,37 +1372,37 @@
         <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6" s="1" t="n">
         <f aca="false">COUNTIF(F6:M6,"P")</f>
@@ -1291,41 +1413,47 @@
         <v>0</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T6,R6,P6,N6,L6),0)</f>
         <v>7</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z6" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC6" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH6" s="0" t="n">
-        <v>8</v>
+      <c r="AG6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1333,37 +1461,37 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N7" s="1" t="n">
         <f aca="false">COUNTIF(F7:M7,"P")</f>
@@ -1374,50 +1502,56 @@
         <v>0</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T7,R7,P7,N7,L7),0)</f>
         <v>6</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF7" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH7" s="0" t="n">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,37 +1559,37 @@
         <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N8" s="1" t="n">
         <f aca="false">COUNTIF(F8:M8,"P")</f>
@@ -1466,10 +1600,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T8,R8,P8,N8,L8),0)</f>
@@ -1479,40 +1613,46 @@
         <v>6</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC8" s="1" t="n">
         <v>3</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF8" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AG8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AG8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="AI8" s="5" t="s">
-        <v>44</v>
+      <c r="AI8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1520,37 +1660,37 @@
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N9" s="1" t="n">
         <f aca="false">COUNTIF(F9:M9,"P")</f>
@@ -1561,40 +1701,46 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T9,R9,P9,N9,L9),0)</f>
         <v>3</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AG9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AG9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1603,37 +1749,37 @@
         <v>1</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N10" s="1" t="n">
         <f aca="false">COUNTIF(F10:M10,"P")</f>
@@ -1644,46 +1790,52 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="W10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF10" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH10" s="0" t="n">
-        <v>8</v>
+      <c r="AG10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1691,37 +1843,37 @@
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N11" s="1" t="n">
         <f aca="false">COUNTIF(F11:M11,"P")</f>
@@ -1732,41 +1884,47 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T11,R11,P11,N11,L11),0)</f>
         <v>5</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z11" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF11" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH11" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI11" s="5" t="s">
-        <v>59</v>
+      <c r="AG11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1774,37 +1932,37 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N12" s="1" t="n">
         <f aca="false">COUNTIF(F12:M12,"P")</f>
@@ -1815,47 +1973,53 @@
         <v>0</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T12,R12,P12,N12,L12),0)</f>
         <v>7</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC12" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH12" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI12" s="5" t="s">
-        <v>65</v>
+      <c r="AG12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1863,37 +2027,37 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N13" s="1" t="n">
         <f aca="false">COUNTIF(F13:M13,"P")</f>
@@ -1904,44 +2068,50 @@
         <v>0</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T13,R13,P13,N13,L13),0)</f>
         <v>7</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z13" s="1" t="n">
         <v>6</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC13" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH13" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI13" s="5" t="s">
-        <v>70</v>
+      <c r="AG13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,37 +2119,37 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N14" s="1" t="n">
         <f aca="false">COUNTIF(F14:M14,"P")</f>
@@ -1990,38 +2160,44 @@
         <v>0</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T14,R14,P14,N14,L14),0)</f>
         <v>6</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC14" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH14" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="5" t="s">
-        <v>74</v>
+      <c r="AG14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2029,40 +2205,40 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N15" s="1" t="n">
         <f aca="false">COUNTIF(F15:M15,"P")</f>
@@ -2073,56 +2249,62 @@
         <v>0</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T15,R15,P15,N15,L15),0)</f>
         <v>4</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC15" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH15" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI15" s="5" t="s">
-        <v>84</v>
+      <c r="AG15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2130,37 +2312,37 @@
         <v>10</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N16" s="1" t="n">
         <f aca="false">COUNTIF(F16:M16,"P")</f>
@@ -2171,35 +2353,41 @@
         <v>0</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T16,R16,P16,N16,L16),0)</f>
         <v>6</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH16" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI16" s="5" t="s">
-        <v>89</v>
+        <v>15</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2207,40 +2395,40 @@
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N17" s="1" t="n">
         <f aca="false">COUNTIF(F17:M17,"P")</f>
@@ -2251,40 +2439,46 @@
         <v>1</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T17,R17,P17,N17,L17),0)</f>
         <v>5</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH17" s="0" t="n">
+      <c r="AG17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK17" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2293,37 +2487,37 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N18" s="1" t="n">
         <f aca="false">COUNTIF(F18:M18,"P")</f>
@@ -2334,34 +2528,40 @@
         <v>0</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T18,R18,P18,N18,L18),0)</f>
         <v>7</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH18" s="0" t="n">
+      <c r="AG18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK18" s="1" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2416,6 +2616,10 @@
       </c>
       <c r="AG19" s="1" t="n">
         <f aca="false">COUNTIF(AG3:AG18,"P")</f>
+        <v>13</v>
+      </c>
+      <c r="AJ19" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ18,"P")</f>
         <v>13</v>
       </c>
     </row>
@@ -2435,12 +2639,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr defaultColWidth="9.5625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="14.7"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="5" min="4" style="1" width="9.36"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="6" min="6" style="1" width="15.7"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="10.7"/>
@@ -2461,8 +2665,12 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="25" style="1" width="9.55"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="1" width="56.3"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="9.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="65.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="20.92"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="29" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="65.64"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="33" min="31" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="34" style="0" width="9.56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="35" min="35" style="1" width="20.92"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="37" min="36" style="0" width="9.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2485,37 +2693,37 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>5</v>
@@ -2533,10 +2741,10 @@
         <v>5</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>45898</v>
@@ -2565,133 +2773,151 @@
       <c r="AF2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AG2" s="4" t="n">
+      <c r="AG2" s="3" t="n">
         <v>45947</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AH2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI2" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
+        <v>45961</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL2" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>8</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I3" s="1" t="n">
         <f aca="false">G3+H3/2</f>
-        <v>9</v>
-      </c>
-      <c r="J3" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D3:F3,I3),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K3" s="6" t="str">
+        <v>5</v>
+      </c>
+      <c r="K3" s="1" t="str">
         <f aca="false">IF(J3&lt;7,"TEP","TEA")</f>
-        <v>TEA</v>
+        <v>TEP</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>7</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N3" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="T3" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U3" s="6" t="n">
-        <f aca="false">ROUND(AVERAGE(T3,R3,P3,N3,L3),0)</f>
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="U3" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="W3" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Z3" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC3" s="1" t="n">
         <v>9</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF3" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH3" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK3" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL3" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK3,AH3,AF3,AC3,Z3,W3,C3),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>8</v>
@@ -2709,98 +2935,114 @@
         <f aca="false">G4+H4/2</f>
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D4:F4,I4),0)</f>
         <v>6</v>
       </c>
-      <c r="K4" s="6" t="str">
+      <c r="K4" s="1" t="str">
         <f aca="false">IF(J4&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N4" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="T4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T4,R4,P4,N4,L4),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z4" s="1" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC4" s="1" t="n">
         <v>9</v>
       </c>
+      <c r="AD4" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="AE4" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AF4" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH4" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL4" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK4,AH4,AF4,AC4,Z4,W4,C4),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>7</v>
-      </c>
       <c r="E5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="n">
         <f aca="false">G5+H5/2</f>
-        <v>8</v>
-      </c>
-      <c r="J5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D5:F5,I5),0)</f>
         <v>8</v>
       </c>
-      <c r="K5" s="6" t="str">
+      <c r="K5" s="1" t="str">
         <f aca="false">IF(J5&lt;7,"TEP","TEA")</f>
         <v>TEA</v>
       </c>
@@ -2808,64 +3050,89 @@
         <v>7</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>8</v>
       </c>
+      <c r="O5" s="1" t="s">
+        <v>115</v>
+      </c>
       <c r="P5" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T5" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T5,R5,P5,N5,L5),0)</f>
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Z5" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH5" s="0" t="n">
+      <c r="AG5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL5" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK5,AH5,AF5,AC5,Z5,W5,C5),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>7</v>
@@ -2886,17 +3153,20 @@
         <f aca="false">G6+H6/2</f>
         <v>8</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D6:F6,I6),0)</f>
         <v>6</v>
       </c>
-      <c r="K6" s="6" t="str">
+      <c r="K6" s="1" t="str">
         <f aca="false">IF(J6&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L6" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="M6" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="N6" s="1" t="n">
         <v>8</v>
       </c>
@@ -2904,368 +3174,411 @@
         <v>6</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T6" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T6,R6,P6,N6,L6),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="Z6" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC6" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AG6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL6" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK6,AH6,AF6,AC6,Z6,W6,C6),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="1" t="n">
         <f aca="false">G7+H7/2</f>
-        <v>1</v>
-      </c>
-      <c r="J7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D7:F7,I7),0)</f>
-        <v>3</v>
-      </c>
-      <c r="K7" s="6" t="str">
+        <v>8</v>
+      </c>
+      <c r="K7" s="1" t="str">
         <f aca="false">IF(J7&lt;7,"TEP","TEA")</f>
-        <v>TEP</v>
+        <v>TEA</v>
       </c>
       <c r="L7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>8</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>115</v>
+        <v>15</v>
       </c>
       <c r="T7" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U7" s="6" t="n">
+      <c r="U7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T7,R7,P7,N7,L7),0)</f>
         <v>8</v>
       </c>
-      <c r="V7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="Y7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AA7" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC7" s="1" t="n">
         <v>7</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF7" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH7" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL7" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK7,AH7,AF7,AC7,Z7,W7,C7),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="1" t="n">
         <f aca="false">G8+H8/2</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J8" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D8:F8,I8),0)</f>
-        <v>2</v>
-      </c>
-      <c r="K8" s="6" t="str">
+        <v>5</v>
+      </c>
+      <c r="K8" s="1" t="str">
         <f aca="false">IF(J8&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="N8" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="T8" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T8,R8,P8,N8,L8),0)</f>
-        <v>7</v>
-      </c>
-      <c r="W8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC8" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH8" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI8" s="5" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="AF8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AJ8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK8" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL8" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK8,AH8,AF8,AC8,Z8,W8,C8),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="1" t="n">
         <f aca="false">G9+H9/2</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D9:F9,I9),0)</f>
-        <v>2</v>
-      </c>
-      <c r="K9" s="6" t="str">
+        <v>6</v>
+      </c>
+      <c r="K9" s="1" t="str">
         <f aca="false">IF(J9&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L9" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="N9" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="T9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T9,R9,P9,N9,L9),0)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>26</v>
+        <v>81</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AC9" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AF9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH9" s="0" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AJ9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK9" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL9" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK9,AH9,AF9,AC9,Z9,W9,C9),0)</f>
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="1" t="n">
         <f aca="false">G10+H10/2</f>
-        <v>8</v>
-      </c>
-      <c r="J10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D10:F10,I10),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K10" s="6" t="str">
+        <v>3</v>
+      </c>
+      <c r="K10" s="1" t="str">
         <f aca="false">IF(J10&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
@@ -3273,87 +3586,92 @@
         <v>7</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U10" s="6" t="n">
-        <v>6</v>
+      <c r="U10" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(T10,R10,P10,N10,L10),0)</f>
+        <v>8</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="W10" s="1" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z10" s="1" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC10" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF10" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL10" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK10,AH10,AF10,AC10,Z10,W10,C10),0)</f>
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="n">
         <v>8</v>
@@ -3365,20 +3683,17 @@
         <f aca="false">G11+H11/2</f>
         <v>8</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D11:F11,I11),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K11" s="6" t="str">
+        <v>8</v>
+      </c>
+      <c r="K11" s="1" t="str">
         <f aca="false">IF(J11&lt;7,"TEP","TEA")</f>
-        <v>TEP</v>
+        <v>TEA</v>
       </c>
       <c r="L11" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="N11" s="1" t="n">
         <v>7</v>
       </c>
@@ -3386,61 +3701,71 @@
         <v>8</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="T11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T11,R11,P11,N11,L11),0)</f>
         <v>8</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="Z11" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC11" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF11" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH11" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI11" s="5" t="s">
-        <v>59</v>
+        <v>8</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL11" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK11,AH11,AF11,AC11,Z11,W11,C11),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="n">
         <v>8</v>
@@ -3458,91 +3783,104 @@
         <f aca="false">G12+H12/2</f>
         <v>8</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D12:F12,I12),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K12" s="6" t="str">
+        <v>6</v>
+      </c>
+      <c r="K12" s="1" t="str">
         <f aca="false">IF(J12&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>7</v>
       </c>
+      <c r="O12" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="P12" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="U12" s="6" t="n">
+      <c r="U12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T12,R12,P12,N12,L12),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z12" s="1" t="n">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AC12" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG12" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH12" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI12" s="5" t="s">
-        <v>65</v>
+      <c r="AG12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL12" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK12,AH12,AF12,AC12,Z12,W12,C12),0)</f>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1" t="n">
         <v>8</v>
@@ -3554,13 +3892,13 @@
         <f aca="false">G13+H13/2</f>
         <v>8</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D13:F13,I13),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K13" s="6" t="str">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1" t="str">
         <f aca="false">IF(J13&lt;7,"TEP","TEA")</f>
-        <v>TEA</v>
+        <v>TEP</v>
       </c>
       <c r="L13" s="1" t="n">
         <v>8</v>
@@ -3572,67 +3910,71 @@
         <v>8</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="T13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T13,R13,P13,N13,L13),0)</f>
         <v>8</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z13" s="1" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" s="1" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH13" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI13" s="5" t="s">
-        <v>70</v>
+        <v>7</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL13" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK13,AH13,AF13,AC13,Z13,W13,C13),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>8</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G14" s="1" t="n">
         <v>8</v>
@@ -3644,73 +3986,86 @@
         <f aca="false">G14+H14/2</f>
         <v>8</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D14:F14,I14),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K14" s="6" t="str">
+        <v>7</v>
+      </c>
+      <c r="K14" s="1" t="str">
         <f aca="false">IF(J14&lt;7,"TEP","TEA")</f>
-        <v>TEP</v>
+        <v>TEA</v>
       </c>
       <c r="L14" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>7</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="U14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T14,R14,P14,N14,L14),0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC14" s="0" t="n">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AF14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="AG14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH14" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI14" s="5" t="s">
-        <v>74</v>
+      <c r="AG14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL14" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK14,AH14,AF14,AC14,Z14,W14,C14),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>8</v>
@@ -3722,289 +4077,307 @@
         <v>8</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="1" t="n">
         <f aca="false">G15+H15/2</f>
-        <v>8</v>
-      </c>
-      <c r="J15" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D15:F15,I15),0)</f>
         <v>6</v>
       </c>
-      <c r="K15" s="6" t="str">
+      <c r="K15" s="1" t="str">
         <f aca="false">IF(J15&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="N15" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="P15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>125</v>
+        <v>15</v>
       </c>
       <c r="T15" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T15,R15,P15,N15,L15),0)</f>
         <v>7</v>
       </c>
-      <c r="V15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="W15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="Y15" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Z15" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC15" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH15" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI15" s="5" t="s">
-        <v>84</v>
+        <v>8</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL15" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK15,AH15,AF15,AC15,Z15,W15,C15),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="1" t="n">
         <f aca="false">G16+H16/2</f>
-        <v>8</v>
-      </c>
-      <c r="J16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D16:F16,I16),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K16" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="K16" s="1" t="str">
         <f aca="false">IF(J16&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
       <c r="L16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="N16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="T16" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="U16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T16,R16,P16,N16,L16),0)</f>
         <v>7</v>
       </c>
+      <c r="W16" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="Y16" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AC16" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH16" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI16" s="5" t="s">
-        <v>89</v>
+        <v>2</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK16,AH16,AF16,AC16,Z16,W16,C16),0)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="1" t="n">
         <f aca="false">G17+H17/2</f>
-        <v>8</v>
-      </c>
-      <c r="J17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D17:F17,I17),0)</f>
-        <v>7</v>
-      </c>
-      <c r="K17" s="6" t="str">
+        <v>2</v>
+      </c>
+      <c r="K17" s="1" t="str">
         <f aca="false">IF(J17&lt;7,"TEP","TEA")</f>
-        <v>TEA</v>
+        <v>TEP</v>
       </c>
       <c r="L17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>128</v>
+        <v>1</v>
       </c>
       <c r="N17" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="T17" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T17,R17,P17,N17,L17),0)</f>
-        <v>7</v>
+        <v>4</v>
+      </c>
+      <c r="V17" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AC17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD17" s="1" t="s">
-        <v>93</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="AH17" s="0" t="n">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK17,AH17,AF17,AC17,Z17,W17,C17),0)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>8</v>
@@ -4016,17 +4389,17 @@
         <v>8</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1" t="n">
         <f aca="false">G18+H18/2</f>
-        <v>9</v>
-      </c>
-      <c r="J18" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" s="5" t="n">
         <f aca="false">ROUND(AVERAGE(D18:F18,I18),0)</f>
         <v>6</v>
       </c>
-      <c r="K18" s="6" t="str">
+      <c r="K18" s="1" t="str">
         <f aca="false">IF(J18&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
@@ -4034,53 +4407,57 @@
         <v>7</v>
       </c>
       <c r="N18" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P18" s="1" t="n">
         <v>6</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T18" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="U18" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(T18,R18,P18,N18,L18),0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z18" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC18" s="1" t="n">
         <v>8</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="AG18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH18" s="0" t="n">
-        <v>9</v>
+      <c r="AG18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL18" s="6" t="n">
+        <f aca="false">ROUND(AVERAGE(AK18,AH18,AF18,AC18,Z18,W18,C18),0)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4108,27 +4485,43 @@
         <f aca="false">COUNTIF(AG3:AG18,"P")</f>
         <v>13</v>
       </c>
+      <c r="AJ19" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ18,"P")</f>
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="J3:J18">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K18">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"TEP"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:U18">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>4</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL3:AL18">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>4</formula>
+      <formula>6</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4160,22 +4553,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4183,7 +4576,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>1</v>
@@ -4197,16 +4590,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -4220,16 +4613,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>5</v>
@@ -4243,16 +4636,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -4266,16 +4659,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -4289,16 +4682,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3</v>
@@ -4312,16 +4705,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -4340,13 +4733,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -4357,16 +4750,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>2</v>
@@ -4380,16 +4773,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -4403,16 +4796,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7</v>
@@ -4431,13 +4824,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
@@ -4448,16 +4841,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -4471,16 +4864,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>2</v>
@@ -4494,16 +4887,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
@@ -4517,16 +4910,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -4540,7 +4933,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>1</v>
@@ -4554,16 +4947,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -4608,10 +5001,10 @@
         <v>45751</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4619,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="1" t="n">
         <f aca="false">C2+D2</f>
@@ -4634,7 +5027,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" s="1" t="n">
         <f aca="false">C3+D3</f>
@@ -4649,7 +5042,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>2</v>
@@ -4664,7 +5057,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="n">
         <f aca="false">C5+D5</f>
@@ -4676,7 +5069,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="n">
         <f aca="false">C6+D6</f>
@@ -4688,7 +5081,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="1" t="n">
         <f aca="false">C7+D7</f>
@@ -4703,7 +5096,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="1" t="n">
         <f aca="false">C8+D8</f>
@@ -4715,7 +5108,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="n">
         <f aca="false">C9+D9</f>
@@ -4730,7 +5123,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="1" t="n">
         <f aca="false">C10+D10</f>
@@ -4745,7 +5138,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E11" s="1" t="n">
         <f aca="false">C11+D11</f>
@@ -4757,7 +5150,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12" s="1" t="n">
         <f aca="false">C12+D12</f>
@@ -4769,7 +5162,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" s="1" t="n">
         <f aca="false">C13+D13</f>
@@ -4781,7 +5174,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>1</v>
@@ -4799,7 +5192,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" s="1" t="n">
         <f aca="false">C15+D15</f>
@@ -4811,7 +5204,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E16" s="1" t="n">
         <f aca="false">C16+D16</f>
@@ -4823,7 +5216,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E17" s="1" t="n">
         <f aca="false">C17+D17</f>

--- a/inasistencias-4b-elecYsiscom-tp/alumnos-4b-ElecYsisCom-tp.xlsx
+++ b/inasistencias-4b-elecYsiscom-tp/alumnos-4b-ElecYsisCom-tp.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="166">
   <si>
     <t xml:space="preserve">nro</t>
   </si>
@@ -319,6 +319,9 @@
     <t xml:space="preserve">49837749@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">febrero</t>
+  </si>
+  <si>
     <t xml:space="preserve">1-fuentes</t>
   </si>
   <si>
@@ -413,6 +416,9 @@
   </si>
   <si>
     <t xml:space="preserve">separar los bornes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprobado</t>
   </si>
   <si>
     <t xml:space="preserve">aporte de tevez</t>
@@ -550,12 +556,24 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00A933"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -592,7 +610,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -613,11 +631,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -630,54 +664,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCC0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFFCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006600"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -744,7 +731,6 @@
           <bgColor rgb="FFCCFFCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -759,7 +745,6 @@
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
@@ -775,7 +760,6 @@
           <bgColor rgb="FFCC0000"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
   </dxfs>
   <colors>
@@ -829,7 +813,7 @@
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF00A933"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -2639,7 +2623,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AN19"/>
   <sheetFormatPr defaultColWidth="9.5625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.32"/>
@@ -2667,10 +2651,10 @@
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="9.55"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="29" min="29" style="1" width="9.56"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="65.64"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="33" min="31" style="1" width="9.56"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="34" style="0" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="34" min="31" style="1" width="9.56"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="35" min="35" style="1" width="20.92"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="37" min="36" style="0" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="37" min="36" style="1" width="9.56"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="38" min="38" style="0" width="9.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,6 +2665,9 @@
         <v>45835</v>
       </c>
       <c r="V1" s="3"/>
+      <c r="AM1" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -2693,37 +2680,37 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>5</v>
@@ -2741,10 +2728,10 @@
         <v>5</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V2" s="3" t="n">
         <v>45898</v>
@@ -2788,11 +2775,14 @@
       <c r="AK2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AL2" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AL2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AM2" s="5" t="n">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -2821,7 +2811,7 @@
         <f aca="false">G3+H3/2</f>
         <v>8</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D3:F3,I3),0)</f>
         <v>5</v>
       </c>
@@ -2833,7 +2823,7 @@
         <v>7</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>7</v>
@@ -2848,7 +2838,7 @@
         <v>15</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="T3" s="1" t="n">
         <v>9</v>
@@ -2906,7 +2896,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
@@ -2935,7 +2925,7 @@
         <f aca="false">G4+H4/2</f>
         <v>8</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D4:F4,I4),0)</f>
         <v>6</v>
       </c>
@@ -2947,7 +2937,7 @@
         <v>8</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>7</v>
@@ -2962,7 +2952,7 @@
         <v>15</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T4" s="1" t="n">
         <v>10</v>
@@ -3009,7 +2999,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
@@ -3038,7 +3028,7 @@
         <f aca="false">G5+H5/2</f>
         <v>9</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D5:F5,I5),0)</f>
         <v>8</v>
       </c>
@@ -3050,13 +3040,13 @@
         <v>7</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P5" s="1" t="n">
         <v>6</v>
@@ -3124,7 +3114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
@@ -3153,7 +3143,7 @@
         <f aca="false">G6+H6/2</f>
         <v>8</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D6:F6,I6),0)</f>
         <v>6</v>
       </c>
@@ -3165,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N6" s="1" t="n">
         <v>8</v>
@@ -3221,7 +3211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
@@ -3250,7 +3240,7 @@
         <f aca="false">G7+H7/2</f>
         <v>8</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D7:F7,I7),0)</f>
         <v>8</v>
       </c>
@@ -3262,7 +3252,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1" t="n">
         <v>8</v>
@@ -3296,7 +3286,7 @@
         <v>7</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AE7" s="1" t="s">
         <v>15</v>
@@ -3321,7 +3311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
@@ -3350,7 +3340,7 @@
         <f aca="false">G8+H8/2</f>
         <v>8</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D8:F8,I8),0)</f>
         <v>5</v>
       </c>
@@ -3362,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N8" s="1" t="n">
         <v>7</v>
@@ -3377,7 +3367,7 @@
         <v>15</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T8" s="1" t="n">
         <v>9</v>
@@ -3427,7 +3417,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
@@ -3456,7 +3446,7 @@
         <f aca="false">G9+H9/2</f>
         <v>8</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D9:F9,I9),0)</f>
         <v>6</v>
       </c>
@@ -3468,13 +3458,13 @@
         <v>7</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P9" s="1" t="n">
         <v>6</v>
@@ -3486,7 +3476,7 @@
         <v>15</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="T9" s="1" t="n">
         <v>9</v>
@@ -3545,7 +3535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
@@ -3574,7 +3564,7 @@
         <f aca="false">G10+H10/2</f>
         <v>1</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D10:F10,I10),0)</f>
         <v>3</v>
       </c>
@@ -3586,7 +3576,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N10" s="1" t="n">
         <v>8</v>
@@ -3601,7 +3591,7 @@
         <v>27</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T10" s="1" t="n">
         <v>9</v>
@@ -3654,7 +3644,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
@@ -3683,7 +3673,7 @@
         <f aca="false">G11+H11/2</f>
         <v>8</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D11:F11,I11),0)</f>
         <v>8</v>
       </c>
@@ -3754,7 +3744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
@@ -3783,7 +3773,7 @@
         <f aca="false">G12+H12/2</f>
         <v>8</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D12:F12,I12),0)</f>
         <v>6</v>
       </c>
@@ -3795,13 +3785,13 @@
         <v>7</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N12" s="1" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P12" s="1" t="n">
         <v>6</v>
@@ -3813,7 +3803,7 @@
         <v>15</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="T12" s="1" t="n">
         <v>9</v>
@@ -3863,7 +3853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
@@ -3892,7 +3882,7 @@
         <f aca="false">G13+H13/2</f>
         <v>8</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D13:F13,I13),0)</f>
         <v>5</v>
       </c>
@@ -3957,7 +3947,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
@@ -3986,7 +3976,7 @@
         <f aca="false">G14+H14/2</f>
         <v>8</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D14:F14,I14),0)</f>
         <v>7</v>
       </c>
@@ -3998,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N14" s="1" t="n">
         <v>7</v>
@@ -4054,7 +4044,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
@@ -4083,7 +4073,7 @@
         <f aca="false">G15+H15/2</f>
         <v>9</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D15:F15,I15),0)</f>
         <v>6</v>
       </c>
@@ -4129,7 +4119,7 @@
         <v>8</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AE15" s="1" t="s">
         <v>15</v>
@@ -4154,116 +4144,122 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="7" t="n">
         <f aca="false">G16+H16/2</f>
         <v>1</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(D16:F16,I16),0)</f>
-        <v>2</v>
-      </c>
-      <c r="K16" s="1" t="str">
+        <v>5</v>
+      </c>
+      <c r="K16" s="7" t="str">
         <f aca="false">IF(J16&lt;7,"TEP","TEA")</f>
         <v>TEP</v>
       </c>
-      <c r="L16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="T16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="1" t="n">
+      <c r="L16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(T16,R16,P16,N16,L16),0)</f>
         <v>7</v>
       </c>
-      <c r="W16" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="X16" s="1" t="s">
+      <c r="W16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="Y16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z16" s="1" t="n">
+      <c r="Y16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AA16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AB16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC16" s="1" t="n">
+      <c r="AB16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AD16" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF16" s="1" t="n">
+      <c r="AE16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AG16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH16" s="1" t="n">
+      <c r="AG16" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH16" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AI16" s="2" t="s">
+      <c r="AI16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AJ16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AK16" s="1" t="n">
+      <c r="AJ16" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="AL16" s="6" t="n">
+      <c r="AL16" s="10" t="n">
         <f aca="false">ROUND(AVERAGE(AK16,AH16,AF16,AC16,Z16,W16,C16),0)</f>
         <v>3</v>
+      </c>
+      <c r="AM16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN16" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4295,7 +4291,7 @@
         <f aca="false">G17+H17/2</f>
         <v>1</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D17:F17,I17),0)</f>
         <v>2</v>
       </c>
@@ -4319,7 +4315,7 @@
         <v>27</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T17" s="1" t="n">
         <v>1</v>
@@ -4366,7 +4362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.65" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
@@ -4395,7 +4391,7 @@
         <f aca="false">G18+H18/2</f>
         <v>8</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J18" s="6" t="n">
         <f aca="false">ROUND(AVERAGE(D18:F18,I18),0)</f>
         <v>6</v>
       </c>
@@ -4492,36 +4488,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J3:J18">
-    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="2" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3:K18">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEP"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3:U18">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="5" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="6" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL3:AL18">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="cellIs" priority="8" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="cellIs" priority="9" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4553,22 +4549,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4596,10 +4592,10 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>8</v>
@@ -4619,10 +4615,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>5</v>
@@ -4642,10 +4638,10 @@
         <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>7</v>
@@ -4665,10 +4661,10 @@
         <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>7</v>
@@ -4688,10 +4684,10 @@
         <v>62</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>3</v>
@@ -4711,10 +4707,10 @@
         <v>77</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>9</v>
@@ -4736,10 +4732,10 @@
         <v>77</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>1</v>
@@ -4756,10 +4752,10 @@
         <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>2</v>
@@ -4779,10 +4775,10 @@
         <v>68</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>7</v>
@@ -4802,10 +4798,10 @@
         <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>7</v>
@@ -4827,10 +4823,10 @@
         <v>87</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>5</v>
@@ -4847,10 +4843,10 @@
         <v>73</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>1</v>
@@ -4870,10 +4866,10 @@
         <v>92</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>2</v>
@@ -4893,10 +4889,10 @@
         <v>96</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>6</v>
@@ -4916,10 +4912,10 @@
         <v>42</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>1</v>
@@ -4953,10 +4949,10 @@
         <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>7</v>
@@ -5001,10 +4997,10 @@
         <v>45751</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
